--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Riddh\OneDrive\Desktop\CapG\AIVS-JAVA\MCP\FinalCapstoneProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A64D66-A464-41A7-B16E-F625C5C27829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DA9CBB-F945-4F7B-A2AD-8A79160CC9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="444" windowWidth="11244" windowHeight="12516" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DA9CBB-F945-4F7B-A2AD-8A79160CC9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Riddh\OneDrive\Desktop\CapG\AIVS-JAVA\MCP\FinalCapstoneProject\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Riddh\OneDrive\Desktop\CapG\AIVS-JAVA\MCP\CapstoneProject\FinalCapstoneProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DA9CBB-F945-4F7B-A2AD-8A79160CC9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10506B3F-6622-4D6C-99A9-2582431A107F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="100">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -315,9 +315,6 @@
   </si>
   <si>
     <t>DELETE_NOTE</t>
-  </si>
-  <si>
-    <t>INVALID_NOTE_ID</t>
   </si>
   <si>
     <t>GET_NOTES</t>
@@ -1351,7 +1348,7 @@
         <v>400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1391,7 +1388,7 @@
         <v>400</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1426,14 +1423,14 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>95</v>
+      <c r="F8" s="2">
+        <v>25</v>
       </c>
       <c r="G8" s="2">
         <v>401</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1441,7 +1438,7 @@
         <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1451,7 +1448,7 @@
         <v>401</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1459,7 +1456,7 @@
         <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1469,7 +1466,7 @@
         <v>401</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Riddh\OneDrive\Desktop\CapG\AIVS-JAVA\MCP\CapstoneProject\FinalCapstoneProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10506B3F-6622-4D6C-99A9-2582431A107F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E069786D-4570-4427-80C1-7B9E54F4DB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -74,12 +74,6 @@
     <t>Work</t>
   </si>
   <si>
-    <t>Study</t>
-  </si>
-  <si>
-    <t>Personal</t>
-  </si>
-  <si>
     <t>A101test@mail.com</t>
   </si>
   <si>
@@ -108,9 +102,6 @@
   </si>
   <si>
     <t>Desc A</t>
-  </si>
-  <si>
-    <t>Task</t>
   </si>
   <si>
     <t>Note B</t>
@@ -717,7 +708,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -734,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>7</v>
@@ -745,13 +736,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -762,13 +753,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -828,10 +819,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -839,13 +830,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -856,10 +847,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -867,13 +858,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -881,41 +872,41 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +928,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -952,16 +943,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -970,12 +961,12 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -988,18 +979,18 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
@@ -1008,43 +999,43 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1072,7 +1063,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1081,59 +1072,59 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1150,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -1171,71 +1162,71 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1261,10 +1252,10 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1276,25 +1267,25 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -1304,18 +1295,18 @@
         <v>400</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -1326,21 +1317,21 @@
         <v>400</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1348,15 +1339,15 @@
         <v>400</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1368,19 +1359,19 @@
         <v>400</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1388,37 +1379,37 @@
         <v>400</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2">
         <v>401</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1430,15 +1421,15 @@
         <v>401</v>
       </c>
       <c r="H8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1448,15 +1439,15 @@
         <v>401</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1466,7 +1457,7 @@
         <v>401</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
